--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123968082</v>
+        <v>123967562</v>
       </c>
       <c r="B2" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472627</v>
+        <v>472795</v>
       </c>
       <c r="R2" t="n">
-        <v>7078354</v>
+        <v>7078319</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +770,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +794,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123968387</v>
+        <v>123968110</v>
       </c>
       <c r="B3" t="n">
-        <v>90986</v>
+        <v>79869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,27 +843,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -862,13 +872,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472575</v>
+        <v>472609</v>
       </c>
       <c r="R3" t="n">
-        <v>7078376</v>
+        <v>7078359</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +907,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +917,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,22 +936,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -959,10 +969,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123968194</v>
+        <v>123968082</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>79898</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -971,36 +981,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1009,13 +1014,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472648</v>
+        <v>472627</v>
       </c>
       <c r="R4" t="n">
-        <v>7078385</v>
+        <v>7078354</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1044,7 +1049,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,12 +1059,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,22 +1078,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123968062</v>
+        <v>123967787</v>
       </c>
       <c r="B5" t="n">
-        <v>79870</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,37 +1127,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472627</v>
+        <v>472717</v>
       </c>
       <c r="R5" t="n">
-        <v>7078363</v>
+        <v>7078333</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1186,7 +1196,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1196,7 +1206,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,22 +1230,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1400,10 +1415,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967339</v>
+        <v>123967054</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>79870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1416,32 +1431,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1450,13 +1460,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472903</v>
+        <v>472921</v>
       </c>
       <c r="R7" t="n">
-        <v>7078308</v>
+        <v>7078379</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1485,7 +1495,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1495,12 +1505,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1519,22 +1524,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1552,7 +1557,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123967142</v>
+        <v>123966919</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1592,13 +1597,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472921</v>
+        <v>472943</v>
       </c>
       <c r="R8" t="n">
-        <v>7078320</v>
+        <v>7078321</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1627,7 +1632,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1637,12 +1642,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1694,10 +1694,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123967117</v>
+        <v>123968695</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1710,34 +1710,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472917</v>
+        <v>472621</v>
       </c>
       <c r="R9" t="n">
-        <v>7078367</v>
+        <v>7078391</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1769,7 +1774,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1779,7 +1784,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1798,22 +1803,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1968,10 +1973,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123967562</v>
+        <v>123968387</v>
       </c>
       <c r="B11" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1984,32 +1989,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2018,13 +2018,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472795</v>
+        <v>472575</v>
       </c>
       <c r="R11" t="n">
-        <v>7078319</v>
+        <v>7078376</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2063,12 +2063,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2097,12 +2092,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2120,10 +2115,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123967054</v>
+        <v>123968194</v>
       </c>
       <c r="B12" t="n">
-        <v>79870</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2136,27 +2131,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472921</v>
+        <v>472648</v>
       </c>
       <c r="R12" t="n">
-        <v>7078379</v>
+        <v>7078385</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2210,7 +2210,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2229,22 +2234,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2262,10 +2267,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123968695</v>
+        <v>123967590</v>
       </c>
       <c r="B13" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2278,42 +2283,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472621</v>
+        <v>472812</v>
       </c>
       <c r="R13" t="n">
-        <v>7078391</v>
+        <v>7078349</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2352,7 +2352,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ymnigt.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2366,7 +2371,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2381,12 +2386,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2404,10 +2409,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123968110</v>
+        <v>123968062</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2420,42 +2425,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472609</v>
+        <v>472627</v>
       </c>
       <c r="R14" t="n">
-        <v>7078359</v>
+        <v>7078363</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2546,10 +2546,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123966919</v>
+        <v>123967117</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2562,21 +2562,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472943</v>
+        <v>472917</v>
       </c>
       <c r="R15" t="n">
-        <v>7078321</v>
+        <v>7078367</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2650,22 +2650,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123967787</v>
+        <v>123967339</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472717</v>
+        <v>472903</v>
       </c>
       <c r="R16" t="n">
-        <v>7078333</v>
+        <v>7078308</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2835,7 +2835,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123967590</v>
+        <v>123967142</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472812</v>
+        <v>472921</v>
       </c>
       <c r="R17" t="n">
-        <v>7078349</v>
+        <v>7078320</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ymnigt.</t>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1263,10 +1263,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967501</v>
+        <v>123967054</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>79870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1279,32 +1279,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,10 +1308,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472811</v>
+        <v>472921</v>
       </c>
       <c r="R6" t="n">
-        <v>7078319</v>
+        <v>7078379</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
@@ -1348,7 +1343,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1358,12 +1353,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1377,27 +1367,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1415,10 +1405,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967054</v>
+        <v>123967501</v>
       </c>
       <c r="B7" t="n">
-        <v>79870</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1431,27 +1421,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1460,10 +1455,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472921</v>
+        <v>472811</v>
       </c>
       <c r="R7" t="n">
-        <v>7078379</v>
+        <v>7078319</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1495,7 +1490,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1505,7 +1500,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1519,27 +1519,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -2975,6 +2975,757 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124025511</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79869</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>473024</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7078467</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124025513</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57602</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>473007</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7078286</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>upprörda över hökuggla</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124025502</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>472549</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7078358</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124025509</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>472664</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7078416</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124025518</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91557</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>760</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>473028</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7078477</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124025514</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>472767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7078542</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124025503</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>472969</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7078321</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -827,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123968110</v>
+        <v>123968656</v>
       </c>
       <c r="B3" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -843,42 +843,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472609</v>
+        <v>472617</v>
       </c>
       <c r="R3" t="n">
-        <v>7078359</v>
+        <v>7078397</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -917,7 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,22 +931,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -969,10 +964,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123968082</v>
+        <v>123967339</v>
       </c>
       <c r="B4" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,31 +976,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472627</v>
+        <v>472903</v>
       </c>
       <c r="R4" t="n">
-        <v>7078354</v>
+        <v>7078308</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1059,7 +1059,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,22 +1083,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1111,10 +1116,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123967787</v>
+        <v>123967590</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1127,47 +1132,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472717</v>
+        <v>472812</v>
       </c>
       <c r="R5" t="n">
-        <v>7078333</v>
+        <v>7078349</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1196,7 +1191,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1206,12 +1201,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Ymnigt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1225,7 +1220,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1240,12 +1235,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1263,10 +1258,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967054</v>
+        <v>123967142</v>
       </c>
       <c r="B6" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1279,29 +1274,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
@@ -1311,10 +1301,10 @@
         <v>472921</v>
       </c>
       <c r="R6" t="n">
-        <v>7078379</v>
+        <v>7078320</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1343,7 +1333,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1353,7 +1343,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1372,22 +1367,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1405,10 +1400,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967501</v>
+        <v>123966919</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1421,44 +1416,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472811</v>
+        <v>472943</v>
       </c>
       <c r="R7" t="n">
-        <v>7078319</v>
+        <v>7078321</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1490,7 +1475,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1500,12 +1485,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1519,7 +1499,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1534,12 +1514,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1557,10 +1537,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123966919</v>
+        <v>123968062</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1573,21 +1553,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1597,13 +1577,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472943</v>
+        <v>472627</v>
       </c>
       <c r="R8" t="n">
-        <v>7078321</v>
+        <v>7078363</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1632,7 +1612,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1642,7 +1622,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1661,22 +1641,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1694,10 +1674,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123968695</v>
+        <v>123968387</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>90986</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1710,21 +1690,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1739,13 +1719,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472621</v>
+        <v>472575</v>
       </c>
       <c r="R9" t="n">
-        <v>7078391</v>
+        <v>7078376</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1774,7 +1754,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1784,7 +1764,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1813,12 +1793,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1836,10 +1816,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123968656</v>
+        <v>123967054</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1852,37 +1832,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472617</v>
+        <v>472921</v>
       </c>
       <c r="R10" t="n">
-        <v>7078397</v>
+        <v>7078379</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1911,7 +1896,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1921,7 +1906,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1940,22 +1925,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1973,10 +1958,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123968387</v>
+        <v>123967117</v>
       </c>
       <c r="B11" t="n">
-        <v>90986</v>
+        <v>79869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1989,42 +1974,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472575</v>
+        <v>472917</v>
       </c>
       <c r="R11" t="n">
-        <v>7078376</v>
+        <v>7078367</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2053,7 +2033,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2063,7 +2043,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2082,22 +2062,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2267,10 +2247,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123967590</v>
+        <v>123968110</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2283,37 +2263,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472812</v>
+        <v>472609</v>
       </c>
       <c r="R13" t="n">
-        <v>7078349</v>
+        <v>7078359</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2342,7 +2327,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2352,12 +2337,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ymnigt.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2371,27 +2351,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2409,10 +2389,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123968062</v>
+        <v>123967787</v>
       </c>
       <c r="B14" t="n">
-        <v>79870</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2425,37 +2405,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472627</v>
+        <v>472717</v>
       </c>
       <c r="R14" t="n">
-        <v>7078363</v>
+        <v>7078333</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2484,7 +2474,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2494,7 +2484,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2513,22 +2508,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2546,10 +2541,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123967117</v>
+        <v>123968082</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>79898</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2558,41 +2553,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472917</v>
+        <v>472627</v>
       </c>
       <c r="R15" t="n">
-        <v>7078367</v>
+        <v>7078354</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2683,10 +2683,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123967339</v>
+        <v>123968695</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2699,32 +2699,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2733,13 +2728,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472903</v>
+        <v>472621</v>
       </c>
       <c r="R16" t="n">
-        <v>7078308</v>
+        <v>7078391</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2768,7 +2763,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2778,12 +2773,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2835,10 +2825,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123967142</v>
+        <v>123967501</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2851,37 +2841,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472921</v>
+        <v>472811</v>
       </c>
       <c r="R17" t="n">
-        <v>7078320</v>
+        <v>7078319</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025513</v>
+        <v>124025518</v>
       </c>
       <c r="B19" t="n">
-        <v>57602</v>
+        <v>91557</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3091,54 +3091,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Norra Skärvången NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473007</v>
+        <v>473028</v>
       </c>
       <c r="R19" t="n">
-        <v>7078286</v>
+        <v>7078477</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3173,17 +3157,13 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>upprörda över hökuggla</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3202,7 +3182,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025502</v>
+        <v>124025503</v>
       </c>
       <c r="B20" t="n">
         <v>57491</v>
@@ -3242,10 +3222,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472549</v>
+        <v>472969</v>
       </c>
       <c r="R20" t="n">
-        <v>7078358</v>
+        <v>7078321</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3282,7 +3262,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3416,10 +3396,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025518</v>
+        <v>124025502</v>
       </c>
       <c r="B22" t="n">
-        <v>91557</v>
+        <v>57491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3428,25 +3408,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3456,10 +3436,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473028</v>
+        <v>472549</v>
       </c>
       <c r="R22" t="n">
-        <v>7078477</v>
+        <v>7078358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3494,13 +3474,17 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3621,10 +3605,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124025503</v>
+        <v>124025513</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
+        <v>57602</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3633,20 +3617,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3654,17 +3638,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Norra Skärvången NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472969</v>
+        <v>473007</v>
       </c>
       <c r="R24" t="n">
-        <v>7078321</v>
+        <v>7078286</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>upprörda över hökuggla</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -827,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123968656</v>
+        <v>123967339</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -843,37 +843,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472617</v>
+        <v>472903</v>
       </c>
       <c r="R3" t="n">
-        <v>7078397</v>
+        <v>7078308</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +912,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +922,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,12 +956,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,10 +979,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123967339</v>
+        <v>123968656</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -980,47 +995,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472903</v>
+        <v>472617</v>
       </c>
       <c r="R4" t="n">
-        <v>7078308</v>
+        <v>7078397</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1049,7 +1054,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1059,12 +1064,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025502</v>
+        <v>124025514</v>
       </c>
       <c r="B22" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472549</v>
+        <v>472767</v>
       </c>
       <c r="R22" t="n">
-        <v>7078358</v>
+        <v>7078542</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3472,11 +3472,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3503,10 +3498,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025514</v>
+        <v>124025502</v>
       </c>
       <c r="B23" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3519,21 +3514,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472767</v>
+        <v>472549</v>
       </c>
       <c r="R23" t="n">
-        <v>7078542</v>
+        <v>7078358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3579,6 +3574,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123967562</v>
+        <v>123968387</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -725,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472795</v>
+        <v>472575</v>
       </c>
       <c r="R2" t="n">
-        <v>7078319</v>
+        <v>7078376</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +794,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -827,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967339</v>
+        <v>123968062</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>79870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -843,47 +833,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472903</v>
+        <v>472627</v>
       </c>
       <c r="R3" t="n">
-        <v>7078308</v>
+        <v>7078363</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -912,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -922,12 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -946,22 +921,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -979,7 +954,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123968656</v>
+        <v>123967142</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -1019,13 +994,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472617</v>
+        <v>472921</v>
       </c>
       <c r="R4" t="n">
-        <v>7078397</v>
+        <v>7078320</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1054,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1064,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1116,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123967590</v>
+        <v>123967117</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1132,21 +1112,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1156,13 +1136,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472812</v>
+        <v>472917</v>
       </c>
       <c r="R5" t="n">
-        <v>7078349</v>
+        <v>7078367</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1191,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1201,12 +1181,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ymnigt.</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1220,27 +1195,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1258,10 +1233,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967142</v>
+        <v>123967787</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1274,37 +1249,47 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472921</v>
+        <v>472717</v>
       </c>
       <c r="R6" t="n">
-        <v>7078320</v>
+        <v>7078333</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1333,7 +1318,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1343,12 +1328,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1377,12 +1362,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1400,10 +1385,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123966919</v>
+        <v>123967339</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1416,37 +1401,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472943</v>
+        <v>472903</v>
       </c>
       <c r="R7" t="n">
-        <v>7078321</v>
+        <v>7078308</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1475,7 +1470,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1485,7 +1480,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123968062</v>
+        <v>123968082</v>
       </c>
       <c r="B8" t="n">
-        <v>79870</v>
+        <v>79898</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1549,28 +1549,33 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
@@ -1580,10 +1585,10 @@
         <v>472627</v>
       </c>
       <c r="R8" t="n">
-        <v>7078363</v>
+        <v>7078354</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1622,7 +1627,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1674,10 +1679,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123968387</v>
+        <v>123968194</v>
       </c>
       <c r="B9" t="n">
-        <v>90986</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1690,27 +1695,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1719,13 +1729,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472575</v>
+        <v>472648</v>
       </c>
       <c r="R9" t="n">
-        <v>7078376</v>
+        <v>7078385</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1754,7 +1764,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1764,7 +1774,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1793,12 +1808,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1816,10 +1831,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123967054</v>
+        <v>123968656</v>
       </c>
       <c r="B10" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1832,42 +1847,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472921</v>
+        <v>472617</v>
       </c>
       <c r="R10" t="n">
-        <v>7078379</v>
+        <v>7078397</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1896,7 +1906,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1906,7 +1916,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1925,22 +1935,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1958,10 +1968,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123967117</v>
+        <v>123967054</v>
       </c>
       <c r="B11" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1974,37 +1984,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472917</v>
+        <v>472921</v>
       </c>
       <c r="R11" t="n">
-        <v>7078367</v>
+        <v>7078379</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2033,7 +2048,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2043,7 +2058,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2095,10 +2110,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123968194</v>
+        <v>123968110</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2111,32 +2126,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2145,13 +2155,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472648</v>
+        <v>472609</v>
       </c>
       <c r="R12" t="n">
-        <v>7078385</v>
+        <v>7078359</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2180,7 +2190,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2190,12 +2200,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2214,22 +2219,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2247,10 +2252,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123968110</v>
+        <v>123968695</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2263,27 +2268,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2292,13 +2297,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472609</v>
+        <v>472621</v>
       </c>
       <c r="R13" t="n">
-        <v>7078359</v>
+        <v>7078391</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2327,7 +2332,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2337,7 +2342,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2356,22 +2361,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2389,10 +2394,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123967787</v>
+        <v>123967590</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2405,47 +2410,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472717</v>
+        <v>472812</v>
       </c>
       <c r="R14" t="n">
-        <v>7078333</v>
+        <v>7078349</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2474,7 +2469,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2484,12 +2479,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Ymnigt.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2503,7 +2498,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2518,12 +2513,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2541,10 +2536,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123968082</v>
+        <v>123967501</v>
       </c>
       <c r="B15" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2553,31 +2548,36 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472627</v>
+        <v>472811</v>
       </c>
       <c r="R15" t="n">
-        <v>7078354</v>
+        <v>7078319</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2631,7 +2631,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2645,27 +2650,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2683,10 +2688,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123968695</v>
+        <v>123966919</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2699,42 +2704,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472621</v>
+        <v>472943</v>
       </c>
       <c r="R16" t="n">
-        <v>7078391</v>
+        <v>7078321</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123967501</v>
+        <v>123967562</v>
       </c>
       <c r="B17" t="n">
         <v>57491</v>
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472811</v>
+        <v>472795</v>
       </c>
       <c r="R17" t="n">
         <v>7078319</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2977,10 +2977,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124025511</v>
+        <v>124025503</v>
       </c>
       <c r="B18" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473024</v>
+        <v>472969</v>
       </c>
       <c r="R18" t="n">
-        <v>7078467</v>
+        <v>7078321</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3053,6 +3053,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3079,10 +3084,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025518</v>
+        <v>124025514</v>
       </c>
       <c r="B19" t="n">
-        <v>91557</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3091,25 +3096,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473028</v>
+        <v>472767</v>
       </c>
       <c r="R19" t="n">
-        <v>7078477</v>
+        <v>7078542</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3163,7 +3168,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3182,10 +3186,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025503</v>
+        <v>124025511</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3198,21 +3202,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3222,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472969</v>
+        <v>473024</v>
       </c>
       <c r="R20" t="n">
-        <v>7078321</v>
+        <v>7078467</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3258,11 +3262,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3396,10 +3395,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025514</v>
+        <v>124025518</v>
       </c>
       <c r="B22" t="n">
-        <v>91008</v>
+        <v>91557</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3408,25 +3407,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3436,10 +3435,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472767</v>
+        <v>473028</v>
       </c>
       <c r="R22" t="n">
-        <v>7078542</v>
+        <v>7078477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3480,6 +3479,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -1537,10 +1537,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123968082</v>
+        <v>123968656</v>
       </c>
       <c r="B8" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1549,46 +1549,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472627</v>
+        <v>472617</v>
       </c>
       <c r="R8" t="n">
-        <v>7078354</v>
+        <v>7078397</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1617,7 +1612,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1627,7 +1622,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1646,22 +1641,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1679,10 +1674,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123968194</v>
+        <v>123968082</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>79898</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1691,36 +1686,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1729,13 +1719,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472648</v>
+        <v>472627</v>
       </c>
       <c r="R9" t="n">
-        <v>7078385</v>
+        <v>7078354</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1764,7 +1754,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1774,12 +1764,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1798,22 +1783,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1831,10 +1816,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123968656</v>
+        <v>123968194</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1847,34 +1832,44 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472617</v>
+        <v>472648</v>
       </c>
       <c r="R10" t="n">
-        <v>7078397</v>
+        <v>7078385</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1906,7 +1901,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1916,7 +1911,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123968387</v>
+        <v>123967117</v>
       </c>
       <c r="B2" t="n">
-        <v>90986</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472575</v>
+        <v>472917</v>
       </c>
       <c r="R2" t="n">
-        <v>7078376</v>
+        <v>7078367</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123968062</v>
+        <v>123968387</v>
       </c>
       <c r="B3" t="n">
-        <v>79870</v>
+        <v>90986</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,37 +828,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472627</v>
+        <v>472575</v>
       </c>
       <c r="R3" t="n">
-        <v>7078363</v>
+        <v>7078376</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,22 +921,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123967142</v>
+        <v>123968695</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,34 +970,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472921</v>
+        <v>472621</v>
       </c>
       <c r="R4" t="n">
-        <v>7078320</v>
+        <v>7078391</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123967117</v>
+        <v>123967142</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472917</v>
+        <v>472921</v>
       </c>
       <c r="R5" t="n">
-        <v>7078367</v>
+        <v>7078320</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,7 +1181,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,22 +1205,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1233,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967787</v>
+        <v>123967590</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,47 +1254,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472717</v>
+        <v>472812</v>
       </c>
       <c r="R6" t="n">
-        <v>7078333</v>
+        <v>7078349</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1318,7 +1313,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1328,12 +1323,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Ymnigt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,7 +1342,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1362,12 +1357,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1385,10 +1380,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967339</v>
+        <v>123967054</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>79870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1401,32 +1396,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1435,13 +1425,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472903</v>
+        <v>472921</v>
       </c>
       <c r="R7" t="n">
-        <v>7078308</v>
+        <v>7078379</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1470,7 +1460,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1480,12 +1470,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1504,22 +1489,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1537,7 +1522,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123968656</v>
+        <v>123966919</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1577,13 +1562,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472617</v>
+        <v>472943</v>
       </c>
       <c r="R8" t="n">
-        <v>7078397</v>
+        <v>7078321</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1612,7 +1597,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1622,7 +1607,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1674,10 +1659,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123968082</v>
+        <v>123967501</v>
       </c>
       <c r="B9" t="n">
-        <v>79898</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1686,31 +1671,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1719,13 +1709,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472627</v>
+        <v>472811</v>
       </c>
       <c r="R9" t="n">
-        <v>7078354</v>
+        <v>7078319</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1754,7 +1744,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1764,7 +1754,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1778,27 +1773,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1816,7 +1811,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123968194</v>
+        <v>123967562</v>
       </c>
       <c r="B10" t="n">
         <v>57491</v>
@@ -1852,7 +1847,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1866,10 +1861,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472648</v>
+        <v>472795</v>
       </c>
       <c r="R10" t="n">
-        <v>7078385</v>
+        <v>7078319</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1901,7 +1896,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1911,12 +1906,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran.</t>
+          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1968,10 +1963,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123967054</v>
+        <v>123968656</v>
       </c>
       <c r="B11" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1984,42 +1979,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472921</v>
+        <v>472617</v>
       </c>
       <c r="R11" t="n">
-        <v>7078379</v>
+        <v>7078397</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2048,7 +2038,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2058,7 +2048,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2077,22 +2067,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2110,10 +2100,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123968110</v>
+        <v>123968194</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2126,27 +2116,32 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2155,13 +2150,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472609</v>
+        <v>472648</v>
       </c>
       <c r="R12" t="n">
-        <v>7078359</v>
+        <v>7078385</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2190,7 +2185,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2200,7 +2195,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2219,22 +2219,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123968695</v>
+        <v>123967787</v>
       </c>
       <c r="B13" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2268,27 +2268,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2297,13 +2302,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472621</v>
+        <v>472717</v>
       </c>
       <c r="R13" t="n">
-        <v>7078391</v>
+        <v>7078333</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2332,7 +2337,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2342,7 +2347,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2394,10 +2404,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123967590</v>
+        <v>123968082</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79898</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2406,41 +2416,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472812</v>
+        <v>472627</v>
       </c>
       <c r="R14" t="n">
-        <v>7078349</v>
+        <v>7078354</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2469,7 +2484,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2479,12 +2494,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ymnigt.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2498,27 +2508,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2536,10 +2546,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123967501</v>
+        <v>123968110</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2552,32 +2562,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2586,10 +2591,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472811</v>
+        <v>472609</v>
       </c>
       <c r="R15" t="n">
-        <v>7078319</v>
+        <v>7078359</v>
       </c>
       <c r="S15" t="n">
         <v>7</v>
@@ -2621,7 +2626,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2631,12 +2636,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2650,27 +2650,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2688,10 +2688,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123966919</v>
+        <v>123968062</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2704,21 +2704,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472943</v>
+        <v>472627</v>
       </c>
       <c r="R16" t="n">
-        <v>7078321</v>
+        <v>7078363</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2792,22 +2792,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123967562</v>
+        <v>123967339</v>
       </c>
       <c r="B17" t="n">
         <v>57491</v>
@@ -2861,7 +2861,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472795</v>
+        <v>472903</v>
       </c>
       <c r="R17" t="n">
-        <v>7078319</v>
+        <v>7078308</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3084,10 +3084,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025514</v>
+        <v>124025518</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>91557</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3096,25 +3096,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472767</v>
+        <v>473028</v>
       </c>
       <c r="R19" t="n">
-        <v>7078542</v>
+        <v>7078477</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3168,6 +3168,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3186,10 +3187,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025511</v>
+        <v>124025514</v>
       </c>
       <c r="B20" t="n">
-        <v>79869</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,21 +3203,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3226,10 +3227,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473024</v>
+        <v>472767</v>
       </c>
       <c r="R20" t="n">
-        <v>7078467</v>
+        <v>7078542</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3288,10 +3289,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025509</v>
+        <v>124025511</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>79869</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3304,21 +3305,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3328,10 +3329,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472664</v>
+        <v>473024</v>
       </c>
       <c r="R21" t="n">
-        <v>7078416</v>
+        <v>7078467</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3364,11 +3365,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3395,10 +3391,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025518</v>
+        <v>124025509</v>
       </c>
       <c r="B22" t="n">
-        <v>91557</v>
+        <v>57507</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3407,25 +3403,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>760</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3435,10 +3431,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473028</v>
+        <v>472664</v>
       </c>
       <c r="R22" t="n">
-        <v>7078477</v>
+        <v>7078416</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3473,13 +3469,17 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123968656</v>
+        <v>123966919</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472617</v>
+        <v>472943</v>
       </c>
       <c r="R2" t="n">
-        <v>7078397</v>
+        <v>7078321</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967054</v>
+        <v>123967562</v>
       </c>
       <c r="B3" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,27 +828,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -857,13 +862,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472921</v>
+        <v>472795</v>
       </c>
       <c r="R3" t="n">
-        <v>7078379</v>
+        <v>7078319</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +907,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,22 +931,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +964,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123968695</v>
+        <v>123968656</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,42 +980,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472621</v>
+        <v>472617</v>
       </c>
       <c r="R4" t="n">
-        <v>7078391</v>
+        <v>7078397</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1039,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1049,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,12 +1078,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,10 +1101,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123967142</v>
+        <v>123968695</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,34 +1117,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472921</v>
+        <v>472621</v>
       </c>
       <c r="R5" t="n">
-        <v>7078320</v>
+        <v>7078391</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1171,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,12 +1191,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,12 +1220,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1390,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967117</v>
+        <v>123968387</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1406,37 +1411,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472917</v>
+        <v>472575</v>
       </c>
       <c r="R7" t="n">
-        <v>7078367</v>
+        <v>7078376</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1465,7 +1475,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1475,7 +1485,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,22 +1504,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,10 +1537,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123968387</v>
+        <v>123968082</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1539,31 +1549,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1572,13 +1582,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472575</v>
+        <v>472627</v>
       </c>
       <c r="R8" t="n">
-        <v>7078376</v>
+        <v>7078354</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1607,7 +1617,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1617,7 +1627,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1636,22 +1646,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1669,10 +1679,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123967562</v>
+        <v>123967590</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1685,47 +1695,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472795</v>
+        <v>472812</v>
       </c>
       <c r="R9" t="n">
-        <v>7078319</v>
+        <v>7078349</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Ymnigt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1798,12 +1798,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123968082</v>
+        <v>123967142</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1833,46 +1833,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472627</v>
+        <v>472921</v>
       </c>
       <c r="R10" t="n">
-        <v>7078354</v>
+        <v>7078320</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1901,7 +1896,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1911,7 +1906,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1930,22 +1930,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123967501</v>
+        <v>123967117</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1979,47 +1979,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472811</v>
+        <v>472917</v>
       </c>
       <c r="R11" t="n">
-        <v>7078319</v>
+        <v>7078367</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2048,7 +2038,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2058,12 +2048,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2077,27 +2062,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2115,10 +2100,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123967590</v>
+        <v>123968062</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2131,21 +2116,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2155,10 +2140,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472812</v>
+        <v>472627</v>
       </c>
       <c r="R12" t="n">
-        <v>7078349</v>
+        <v>7078363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2190,7 +2175,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2200,12 +2185,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ymnigt.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2219,27 +2199,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2257,10 +2237,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123966919</v>
+        <v>123967501</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2273,34 +2253,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472943</v>
+        <v>472811</v>
       </c>
       <c r="R13" t="n">
-        <v>7078321</v>
+        <v>7078319</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2332,7 +2322,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2342,7 +2332,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2356,7 +2351,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2371,12 +2366,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2394,7 +2389,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123967339</v>
+        <v>123968194</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2444,13 +2439,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472903</v>
+        <v>472648</v>
       </c>
       <c r="R14" t="n">
-        <v>7078308</v>
+        <v>7078385</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2479,7 +2474,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2489,12 +2484,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Färska och äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2546,10 +2541,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123968194</v>
+        <v>123968110</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2562,32 +2557,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2596,13 +2586,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472648</v>
+        <v>472609</v>
       </c>
       <c r="R15" t="n">
-        <v>7078385</v>
+        <v>7078359</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2631,7 +2621,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2641,12 +2631,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2665,22 +2650,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2698,7 +2683,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123968062</v>
+        <v>123967054</v>
       </c>
       <c r="B16" t="n">
         <v>79892</v>
@@ -2732,19 +2717,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472627</v>
+        <v>472921</v>
       </c>
       <c r="R16" t="n">
-        <v>7078363</v>
+        <v>7078379</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2773,7 +2763,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2783,7 +2773,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2835,10 +2825,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123968110</v>
+        <v>123967339</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2851,27 +2841,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2880,13 +2875,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472609</v>
+        <v>472903</v>
       </c>
       <c r="R17" t="n">
-        <v>7078359</v>
+        <v>7078308</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2915,7 +2910,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2925,7 +2920,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2944,22 +2944,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124025503</v>
+        <v>124025514</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472969</v>
+        <v>472767</v>
       </c>
       <c r="R18" t="n">
-        <v>7078321</v>
+        <v>7078542</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3053,11 +3053,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3186,10 +3181,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025514</v>
+        <v>124025518</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>91579</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3198,25 +3193,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3226,10 +3221,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472767</v>
+        <v>473028</v>
       </c>
       <c r="R20" t="n">
-        <v>7078542</v>
+        <v>7078477</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3270,6 +3265,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3288,10 +3284,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025518</v>
+        <v>124025509</v>
       </c>
       <c r="B21" t="n">
-        <v>91579</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3300,25 +3296,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3328,10 +3324,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473028</v>
+        <v>472664</v>
       </c>
       <c r="R21" t="n">
-        <v>7078477</v>
+        <v>7078416</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3366,13 +3362,17 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025509</v>
+        <v>124025502</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3407,16 +3407,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472664</v>
+        <v>472549</v>
       </c>
       <c r="R22" t="n">
-        <v>7078416</v>
+        <v>7078358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3498,7 +3498,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025502</v>
+        <v>124025503</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472549</v>
+        <v>472969</v>
       </c>
       <c r="R23" t="n">
-        <v>7078358</v>
+        <v>7078321</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123966919</v>
+        <v>123968194</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472943</v>
+        <v>472648</v>
       </c>
       <c r="R2" t="n">
-        <v>7078321</v>
+        <v>7078385</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +770,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +804,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967562</v>
+        <v>123967590</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,47 +843,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472795</v>
+        <v>472812</v>
       </c>
       <c r="R3" t="n">
-        <v>7078319</v>
+        <v>7078349</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,12 +912,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Ymnigt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,7 +931,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -941,12 +946,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,7 +969,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123968656</v>
+        <v>123966919</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -1004,13 +1009,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472617</v>
+        <v>472943</v>
       </c>
       <c r="R4" t="n">
-        <v>7078397</v>
+        <v>7078321</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,7 +1044,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,7 +1054,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1101,10 +1106,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123968695</v>
+        <v>123967142</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1117,39 +1122,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472621</v>
+        <v>472921</v>
       </c>
       <c r="R5" t="n">
-        <v>7078391</v>
+        <v>7078320</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,7 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1220,12 +1225,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1243,10 +1248,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123967787</v>
+        <v>123968062</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,47 +1264,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472717</v>
+        <v>472627</v>
       </c>
       <c r="R6" t="n">
-        <v>7078333</v>
+        <v>7078363</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1328,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1338,12 +1333,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1362,22 +1352,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1395,10 +1385,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123968387</v>
+        <v>123967501</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1411,27 +1401,32 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1440,13 +1435,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472575</v>
+        <v>472811</v>
       </c>
       <c r="R7" t="n">
-        <v>7078376</v>
+        <v>7078319</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1475,7 +1470,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1485,7 +1480,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123968082</v>
+        <v>123967787</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1549,31 +1549,36 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1582,10 +1587,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472627</v>
+        <v>472717</v>
       </c>
       <c r="R8" t="n">
-        <v>7078354</v>
+        <v>7078333</v>
       </c>
       <c r="S8" t="n">
         <v>6</v>
@@ -1617,7 +1622,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1627,7 +1632,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1646,22 +1656,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1679,10 +1689,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123967590</v>
+        <v>123967562</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1695,37 +1705,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472812</v>
+        <v>472795</v>
       </c>
       <c r="R9" t="n">
-        <v>7078349</v>
+        <v>7078319</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1754,7 +1774,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1764,12 +1784,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ymnigt.</t>
+          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1783,7 +1803,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1798,12 +1818,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1821,10 +1841,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123967142</v>
+        <v>123968082</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1833,41 +1853,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472921</v>
+        <v>472627</v>
       </c>
       <c r="R10" t="n">
-        <v>7078320</v>
+        <v>7078354</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1896,7 +1921,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1906,12 +1931,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1930,22 +1950,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2100,10 +2120,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123968062</v>
+        <v>123968656</v>
       </c>
       <c r="B12" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2116,21 +2136,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2140,13 +2160,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472627</v>
+        <v>472617</v>
       </c>
       <c r="R12" t="n">
-        <v>7078363</v>
+        <v>7078397</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2175,7 +2195,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2185,7 +2205,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2204,22 +2224,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2237,10 +2257,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123967501</v>
+        <v>123967054</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2253,32 +2273,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2287,10 +2302,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472811</v>
+        <v>472921</v>
       </c>
       <c r="R13" t="n">
-        <v>7078319</v>
+        <v>7078379</v>
       </c>
       <c r="S13" t="n">
         <v>7</v>
@@ -2322,7 +2337,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2332,12 +2347,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2351,27 +2361,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2389,10 +2399,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123968194</v>
+        <v>123968695</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2405,32 +2415,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2439,13 +2444,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472648</v>
+        <v>472621</v>
       </c>
       <c r="R14" t="n">
-        <v>7078385</v>
+        <v>7078391</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2474,7 +2479,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2484,12 +2489,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2683,10 +2683,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123967054</v>
+        <v>123968387</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2699,27 +2699,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472921</v>
+        <v>472575</v>
       </c>
       <c r="R16" t="n">
-        <v>7078379</v>
+        <v>7078376</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2792,22 +2792,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124025514</v>
+        <v>124025509</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472767</v>
+        <v>472664</v>
       </c>
       <c r="R18" t="n">
-        <v>7078542</v>
+        <v>7078416</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3053,6 +3053,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3079,10 +3084,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025511</v>
+        <v>124025502</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3095,21 +3100,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473024</v>
+        <v>472549</v>
       </c>
       <c r="R19" t="n">
-        <v>7078467</v>
+        <v>7078358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3155,6 +3160,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3181,10 +3191,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025518</v>
+        <v>124025503</v>
       </c>
       <c r="B20" t="n">
-        <v>91579</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3193,25 +3203,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3221,10 +3231,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473028</v>
+        <v>472969</v>
       </c>
       <c r="R20" t="n">
-        <v>7078477</v>
+        <v>7078321</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3259,13 +3269,17 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3284,10 +3298,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025509</v>
+        <v>124025518</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>91579</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3296,25 +3310,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>760</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3324,10 +3338,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472664</v>
+        <v>473028</v>
       </c>
       <c r="R21" t="n">
-        <v>7078416</v>
+        <v>7078477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3362,17 +3376,13 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3391,10 +3401,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025502</v>
+        <v>124025514</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3407,21 +3417,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3431,10 +3441,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472549</v>
+        <v>472767</v>
       </c>
       <c r="R22" t="n">
-        <v>7078358</v>
+        <v>7078542</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3467,11 +3477,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3498,10 +3503,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025503</v>
+        <v>124025511</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3514,21 +3519,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3538,10 +3543,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472969</v>
+        <v>473024</v>
       </c>
       <c r="R23" t="n">
-        <v>7078321</v>
+        <v>7078467</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3574,11 +3579,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123968194</v>
+        <v>123967339</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472648</v>
+        <v>472903</v>
       </c>
       <c r="R2" t="n">
-        <v>7078385</v>
+        <v>7078308</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran.</t>
+          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -827,10 +827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123967590</v>
+        <v>123968062</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472812</v>
+        <v>472627</v>
       </c>
       <c r="R3" t="n">
-        <v>7078349</v>
+        <v>7078363</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,12 +912,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ymnigt.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,27 +926,27 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -969,10 +964,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123966919</v>
+        <v>123967562</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -985,37 +980,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472943</v>
+        <v>472795</v>
       </c>
       <c r="R4" t="n">
-        <v>7078321</v>
+        <v>7078319</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1044,7 +1049,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1054,7 +1059,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1083,12 +1093,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1106,7 +1116,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123967142</v>
+        <v>123966919</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1146,13 +1156,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472921</v>
+        <v>472943</v>
       </c>
       <c r="R5" t="n">
-        <v>7078320</v>
+        <v>7078321</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1191,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1201,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1248,10 +1253,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123968062</v>
+        <v>123968110</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1264,37 +1269,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472627</v>
+        <v>472609</v>
       </c>
       <c r="R6" t="n">
-        <v>7078363</v>
+        <v>7078359</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1323,7 +1333,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1333,7 +1343,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1537,10 +1547,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123967787</v>
+        <v>123967054</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1553,32 +1563,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1587,13 +1592,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472717</v>
+        <v>472921</v>
       </c>
       <c r="R8" t="n">
-        <v>7078333</v>
+        <v>7078379</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1622,7 +1627,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1632,12 +1637,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123967562</v>
+        <v>123967787</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1725,7 +1725,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1739,13 +1739,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472795</v>
+        <v>472717</v>
       </c>
       <c r="R9" t="n">
-        <v>7078319</v>
+        <v>7078333</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2257,10 +2257,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123967054</v>
+        <v>123967590</v>
       </c>
       <c r="B13" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2273,42 +2273,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472921</v>
+        <v>472812</v>
       </c>
       <c r="R13" t="n">
-        <v>7078379</v>
+        <v>7078349</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2337,7 +2332,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2347,7 +2342,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ymnigt.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2361,27 +2361,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123968695</v>
+        <v>123967142</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2415,39 +2415,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472621</v>
+        <v>472921</v>
       </c>
       <c r="R14" t="n">
-        <v>7078391</v>
+        <v>7078320</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2479,7 +2474,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2489,7 +2484,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123968110</v>
+        <v>123968387</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2557,27 +2557,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2586,13 +2586,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472609</v>
+        <v>472575</v>
       </c>
       <c r="R15" t="n">
-        <v>7078359</v>
+        <v>7078376</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2650,22 +2650,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123968387</v>
+        <v>123968695</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2699,21 +2699,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472575</v>
+        <v>472621</v>
       </c>
       <c r="R16" t="n">
-        <v>7078376</v>
+        <v>7078391</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2825,7 +2825,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123967339</v>
+        <v>123968194</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472903</v>
+        <v>472648</v>
       </c>
       <c r="R17" t="n">
-        <v>7078308</v>
+        <v>7078385</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Färska och äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3084,10 +3084,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025502</v>
+        <v>124025511</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3100,21 +3100,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472549</v>
+        <v>473024</v>
       </c>
       <c r="R19" t="n">
-        <v>7078358</v>
+        <v>7078467</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3160,11 +3160,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3298,10 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025518</v>
+        <v>124025502</v>
       </c>
       <c r="B21" t="n">
-        <v>91579</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3310,25 +3305,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3338,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473028</v>
+        <v>472549</v>
       </c>
       <c r="R21" t="n">
-        <v>7078477</v>
+        <v>7078358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3376,13 +3371,17 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3503,10 +3502,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025511</v>
+        <v>124025518</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>91579</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3515,25 +3514,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3543,10 +3542,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473024</v>
+        <v>473028</v>
       </c>
       <c r="R23" t="n">
-        <v>7078467</v>
+        <v>7078477</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,6 +3586,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123967339</v>
+        <v>123968082</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472903</v>
+        <v>472627</v>
       </c>
       <c r="R2" t="n">
-        <v>7078308</v>
+        <v>7078354</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
@@ -760,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -827,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123968062</v>
+        <v>123966919</v>
       </c>
       <c r="B3" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -843,21 +833,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -867,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472627</v>
+        <v>472943</v>
       </c>
       <c r="R3" t="n">
-        <v>7078363</v>
+        <v>7078321</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -902,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -912,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,22 +921,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123967562</v>
+        <v>123967590</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -980,47 +970,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472795</v>
+        <v>472812</v>
       </c>
       <c r="R4" t="n">
-        <v>7078319</v>
+        <v>7078349</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1049,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1059,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Ymnigt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,7 +1058,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1093,12 +1073,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1116,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123966919</v>
+        <v>123967117</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1132,21 +1112,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1156,13 +1136,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472943</v>
+        <v>472917</v>
       </c>
       <c r="R5" t="n">
-        <v>7078321</v>
+        <v>7078367</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1191,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1201,7 +1181,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1220,22 +1200,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1253,10 +1233,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123968110</v>
+        <v>123968062</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,42 +1249,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472609</v>
+        <v>472627</v>
       </c>
       <c r="R6" t="n">
-        <v>7078359</v>
+        <v>7078363</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1333,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1343,7 +1318,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1395,10 +1370,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967501</v>
+        <v>123967054</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1411,32 +1386,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1445,10 +1415,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472811</v>
+        <v>472921</v>
       </c>
       <c r="R7" t="n">
-        <v>7078319</v>
+        <v>7078379</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1480,7 +1450,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1490,12 +1460,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1509,27 +1474,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1547,10 +1512,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123967054</v>
+        <v>123967562</v>
       </c>
       <c r="B8" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1563,27 +1528,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1592,13 +1562,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472921</v>
+        <v>472795</v>
       </c>
       <c r="R8" t="n">
-        <v>7078379</v>
+        <v>7078319</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1627,7 +1597,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1637,7 +1607,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1656,22 +1631,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1689,10 +1664,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123967787</v>
+        <v>123968695</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1705,32 +1680,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1739,13 +1709,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472717</v>
+        <v>472621</v>
       </c>
       <c r="R9" t="n">
-        <v>7078333</v>
+        <v>7078391</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1774,7 +1744,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1784,12 +1754,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1841,10 +1806,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123968082</v>
+        <v>123968656</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1853,46 +1818,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472627</v>
+        <v>472617</v>
       </c>
       <c r="R10" t="n">
-        <v>7078354</v>
+        <v>7078397</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1921,7 +1881,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1931,7 +1891,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1950,22 +1910,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1983,10 +1943,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123967117</v>
+        <v>123967142</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1999,21 +1959,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -2023,10 +1983,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472917</v>
+        <v>472921</v>
       </c>
       <c r="R11" t="n">
-        <v>7078367</v>
+        <v>7078320</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -2058,7 +2018,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2068,7 +2028,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2087,22 +2052,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2120,10 +2085,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123968656</v>
+        <v>123968194</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2136,34 +2101,44 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472617</v>
+        <v>472648</v>
       </c>
       <c r="R12" t="n">
-        <v>7078397</v>
+        <v>7078385</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
@@ -2195,7 +2170,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2205,7 +2180,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2234,12 +2214,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2257,10 +2237,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123967590</v>
+        <v>123967501</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2273,37 +2253,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472812</v>
+        <v>472811</v>
       </c>
       <c r="R13" t="n">
-        <v>7078349</v>
+        <v>7078319</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2332,7 +2322,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2342,12 +2332,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ymnigt.</t>
+          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2376,12 +2366,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2399,10 +2389,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123967142</v>
+        <v>123967787</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2415,37 +2405,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472921</v>
+        <v>472717</v>
       </c>
       <c r="R14" t="n">
-        <v>7078320</v>
+        <v>7078333</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123968387</v>
+        <v>123967339</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2557,27 +2557,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2586,13 +2591,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472575</v>
+        <v>472903</v>
       </c>
       <c r="R15" t="n">
-        <v>7078376</v>
+        <v>7078308</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2621,7 +2626,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2631,7 +2636,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2660,12 +2670,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2683,10 +2693,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123968695</v>
+        <v>123968110</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2699,27 +2709,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2728,13 +2738,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472621</v>
+        <v>472609</v>
       </c>
       <c r="R16" t="n">
-        <v>7078391</v>
+        <v>7078359</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2763,7 +2773,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2773,7 +2783,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2792,22 +2802,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2825,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123968194</v>
+        <v>123968387</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2841,32 +2851,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2875,13 +2880,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472648</v>
+        <v>472575</v>
       </c>
       <c r="R17" t="n">
-        <v>7078385</v>
+        <v>7078376</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2910,7 +2915,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2920,12 +2925,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gran.</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124025509</v>
+        <v>124025511</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472664</v>
+        <v>473024</v>
       </c>
       <c r="R18" t="n">
-        <v>7078416</v>
+        <v>7078467</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3053,11 +3053,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3084,10 +3079,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025511</v>
+        <v>124025509</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3100,21 +3095,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3124,10 +3119,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473024</v>
+        <v>472664</v>
       </c>
       <c r="R19" t="n">
-        <v>7078467</v>
+        <v>7078416</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3160,6 +3155,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3293,10 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025502</v>
+        <v>124025518</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91579</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3305,25 +3305,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472549</v>
+        <v>473028</v>
       </c>
       <c r="R21" t="n">
-        <v>7078358</v>
+        <v>7078477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3371,17 +3371,13 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3502,10 +3498,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025518</v>
+        <v>124025502</v>
       </c>
       <c r="B23" t="n">
-        <v>91579</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3514,25 +3510,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3542,10 +3538,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473028</v>
+        <v>472549</v>
       </c>
       <c r="R23" t="n">
-        <v>7078477</v>
+        <v>7078358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3580,13 +3576,17 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -1664,10 +1664,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123968695</v>
+        <v>123968656</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1680,42 +1680,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472621</v>
+        <v>472617</v>
       </c>
       <c r="R9" t="n">
-        <v>7078391</v>
+        <v>7078397</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1744,7 +1739,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1754,7 +1749,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1783,12 +1778,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1806,7 +1801,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123968656</v>
+        <v>123967142</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1846,13 +1841,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472617</v>
+        <v>472921</v>
       </c>
       <c r="R10" t="n">
-        <v>7078397</v>
+        <v>7078320</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1891,7 +1886,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123967142</v>
+        <v>123968695</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1959,34 +1959,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472921</v>
+        <v>472621</v>
       </c>
       <c r="R11" t="n">
-        <v>7078320</v>
+        <v>7078391</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -2018,7 +2023,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2028,12 +2033,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123968110</v>
+        <v>123968387</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2709,27 +2709,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2738,13 +2738,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472609</v>
+        <v>472575</v>
       </c>
       <c r="R16" t="n">
-        <v>7078359</v>
+        <v>7078376</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123968387</v>
+        <v>123968110</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2851,27 +2851,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2880,13 +2880,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472575</v>
+        <v>472609</v>
       </c>
       <c r="R17" t="n">
-        <v>7078376</v>
+        <v>7078359</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2944,22 +2944,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025509</v>
+        <v>124025503</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3095,16 +3095,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472664</v>
+        <v>472969</v>
       </c>
       <c r="R19" t="n">
-        <v>7078416</v>
+        <v>7078321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025503</v>
+        <v>124025509</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472969</v>
+        <v>472664</v>
       </c>
       <c r="R20" t="n">
-        <v>7078321</v>
+        <v>7078416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123968082</v>
+        <v>123967590</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472627</v>
+        <v>472812</v>
       </c>
       <c r="R2" t="n">
-        <v>7078354</v>
+        <v>7078349</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ymnigt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +779,27 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123966919</v>
+        <v>123967117</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,21 +833,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472943</v>
+        <v>472917</v>
       </c>
       <c r="R3" t="n">
-        <v>7078321</v>
+        <v>7078367</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,22 +921,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123967590</v>
+        <v>123968082</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,41 +966,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472812</v>
+        <v>472627</v>
       </c>
       <c r="R4" t="n">
-        <v>7078349</v>
+        <v>7078354</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ymnigt.</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,27 +1058,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123967117</v>
+        <v>123967054</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,37 +1112,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472917</v>
+        <v>472921</v>
       </c>
       <c r="R5" t="n">
-        <v>7078367</v>
+        <v>7078379</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1171,7 +1176,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,7 +1186,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1233,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123968062</v>
+        <v>123966919</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,21 +1254,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1273,13 +1278,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472627</v>
+        <v>472943</v>
       </c>
       <c r="R6" t="n">
-        <v>7078363</v>
+        <v>7078321</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1308,7 +1313,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1318,7 +1323,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1337,22 +1342,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1370,10 +1375,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123967054</v>
+        <v>123968695</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1386,27 +1391,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1415,13 +1420,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472921</v>
+        <v>472621</v>
       </c>
       <c r="R7" t="n">
-        <v>7078379</v>
+        <v>7078391</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1450,7 +1455,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1460,7 +1465,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1479,22 +1484,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1512,7 +1517,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123967562</v>
+        <v>123967501</v>
       </c>
       <c r="B8" t="n">
         <v>57513</v>
@@ -1562,13 +1567,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472795</v>
+        <v>472811</v>
       </c>
       <c r="R8" t="n">
         <v>7078319</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1607,12 +1612,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,7 +1631,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1664,10 +1669,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123968656</v>
+        <v>123968062</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1680,21 +1685,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1704,13 +1709,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472617</v>
+        <v>472627</v>
       </c>
       <c r="R9" t="n">
-        <v>7078397</v>
+        <v>7078363</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1739,7 +1744,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1749,7 +1754,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1768,22 +1773,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1801,7 +1806,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123967142</v>
+        <v>123968656</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1841,13 +1846,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472921</v>
+        <v>472617</v>
       </c>
       <c r="R10" t="n">
-        <v>7078320</v>
+        <v>7078397</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1876,7 +1881,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1886,12 +1891,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1943,10 +1943,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123968695</v>
+        <v>123968110</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1959,27 +1959,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472621</v>
+        <v>472609</v>
       </c>
       <c r="R11" t="n">
-        <v>7078391</v>
+        <v>7078359</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123968194</v>
+        <v>123967562</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -2121,7 +2121,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472648</v>
+        <v>472795</v>
       </c>
       <c r="R12" t="n">
-        <v>7078385</v>
+        <v>7078319</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gran.</t>
+          <t>Äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2237,7 +2237,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123967501</v>
+        <v>123967339</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -2273,7 +2273,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2287,13 +2287,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472811</v>
+        <v>472903</v>
       </c>
       <c r="R13" t="n">
-        <v>7078319</v>
+        <v>7078308</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2389,7 +2389,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123967787</v>
+        <v>123968194</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472717</v>
+        <v>472648</v>
       </c>
       <c r="R14" t="n">
-        <v>7078333</v>
+        <v>7078385</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Färska och äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2541,7 +2541,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123967339</v>
+        <v>123967787</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472903</v>
+        <v>472717</v>
       </c>
       <c r="R15" t="n">
-        <v>7078308</v>
+        <v>7078333</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka färska ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>Gott om färska ringhack på en snitslad gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2693,10 +2693,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123968387</v>
+        <v>123967142</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2709,42 +2709,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472575</v>
+        <v>472921</v>
       </c>
       <c r="R16" t="n">
-        <v>7078376</v>
+        <v>7078320</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2773,7 +2768,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2783,7 +2778,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2835,10 +2835,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123968110</v>
+        <v>123968387</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2851,27 +2851,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2880,13 +2880,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472609</v>
+        <v>472575</v>
       </c>
       <c r="R17" t="n">
-        <v>7078359</v>
+        <v>7078376</v>
       </c>
       <c r="S17" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2944,22 +2944,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3079,7 +3079,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025503</v>
+        <v>124025502</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472969</v>
+        <v>472549</v>
       </c>
       <c r="R19" t="n">
-        <v>7078321</v>
+        <v>7078358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025509</v>
+        <v>124025503</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472664</v>
+        <v>472969</v>
       </c>
       <c r="R20" t="n">
-        <v>7078416</v>
+        <v>7078321</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025514</v>
+        <v>124025509</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3412,21 +3412,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472767</v>
+        <v>472664</v>
       </c>
       <c r="R22" t="n">
-        <v>7078542</v>
+        <v>7078416</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3472,6 +3472,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3498,10 +3503,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025502</v>
+        <v>124025514</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3514,21 +3519,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3538,10 +3543,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472549</v>
+        <v>472767</v>
       </c>
       <c r="R23" t="n">
-        <v>7078358</v>
+        <v>7078542</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3574,11 +3579,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -1517,10 +1517,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123967501</v>
+        <v>123968062</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1533,47 +1533,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472811</v>
+        <v>472627</v>
       </c>
       <c r="R8" t="n">
-        <v>7078319</v>
+        <v>7078363</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1602,7 +1592,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1612,12 +1602,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1631,27 +1616,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1669,10 +1654,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123968062</v>
+        <v>123967501</v>
       </c>
       <c r="B9" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1685,37 +1670,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nordibodarna, Nordibodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472627</v>
+        <v>472811</v>
       </c>
       <c r="R9" t="n">
-        <v>7078363</v>
+        <v>7078319</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1744,7 +1739,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1754,7 +1749,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka äldre ringhack på en gran med kådaflöden som står vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1768,27 +1768,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 52079-2024 artfynd.xlsx
+++ b/artfynd/A 52079-2024 artfynd.xlsx
@@ -2977,10 +2977,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124025511</v>
+        <v>124025509</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2993,21 +2993,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473024</v>
+        <v>472664</v>
       </c>
       <c r="R18" t="n">
-        <v>7078467</v>
+        <v>7078416</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3053,6 +3053,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3079,7 +3084,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025502</v>
+        <v>124025503</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472549</v>
+        <v>472969</v>
       </c>
       <c r="R19" t="n">
-        <v>7078358</v>
+        <v>7078321</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3159,7 +3164,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3186,10 +3191,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025503</v>
+        <v>124025514</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,21 +3207,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3226,10 +3231,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472969</v>
+        <v>472767</v>
       </c>
       <c r="R20" t="n">
-        <v>7078321</v>
+        <v>7078542</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3262,11 +3267,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,10 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025518</v>
+        <v>124025511</v>
       </c>
       <c r="B21" t="n">
-        <v>91579</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3305,25 +3305,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473028</v>
+        <v>473024</v>
       </c>
       <c r="R21" t="n">
-        <v>7078477</v>
+        <v>7078467</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3377,7 +3377,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3396,10 +3395,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025509</v>
+        <v>124025518</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>91579</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3408,25 +3407,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>760</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3436,10 +3435,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472664</v>
+        <v>473028</v>
       </c>
       <c r="R22" t="n">
-        <v>7078416</v>
+        <v>7078477</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3474,17 +3473,13 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3503,10 +3498,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025514</v>
+        <v>124025502</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3519,21 +3514,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3543,10 +3538,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472767</v>
+        <v>472549</v>
       </c>
       <c r="R23" t="n">
-        <v>7078542</v>
+        <v>7078358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3579,6 +3574,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
